--- a/docs/downloads/11/tbl_cultures_touchees_marovoay_ampijoroa.xlsx
+++ b/docs/downloads/11/tbl_cultures_touchees_marovoay_ampijoroa.xlsx
@@ -549,12 +549,6 @@
           <t>Black Eyes</t>
         </is>
       </c>
-      <c r="C11">
-        <v>4</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -567,12 +561,6 @@
           <t>Courge</t>
         </is>
       </c>
-      <c r="C12">
-        <v>4</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -585,12 +573,6 @@
           <t>cane à sucre</t>
         </is>
       </c>
-      <c r="C13">
-        <v>3</v>
-      </c>
-      <c r="D13">
-        <v>3.6</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -603,12 +585,6 @@
           <t>Brède</t>
         </is>
       </c>
-      <c r="C14">
-        <v>3</v>
-      </c>
-      <c r="D14">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -621,12 +597,6 @@
           <t>Concombre</t>
         </is>
       </c>
-      <c r="C15">
-        <v>3</v>
-      </c>
-      <c r="D15">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -639,12 +609,6 @@
           <t>Black Eyes</t>
         </is>
       </c>
-      <c r="C16">
-        <v>2</v>
-      </c>
-      <c r="D16">
-        <v>2.4</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -657,12 +621,6 @@
           <t>Banane</t>
         </is>
       </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17">
-        <v>1.2</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -675,12 +633,6 @@
           <t>Brède</t>
         </is>
       </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18">
-        <v>1.2</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -692,12 +644,6 @@
         <is>
           <t>arachide</t>
         </is>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19">
-        <v>1.2</v>
       </c>
     </row>
   </sheetData>
